--- a/EXP/1300_50_FFCUnet/results/train/val_result.xlsx
+++ b/EXP/1300_50_FFCUnet/results/train/val_result.xlsx
@@ -450,13 +450,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.3338</v>
+        <v>1.33184</v>
       </c>
       <c r="C2" t="n">
-        <v>0.40716</v>
+        <v>0.52951</v>
       </c>
       <c r="D2" t="n">
-        <v>0.53749</v>
+        <v>0.64591</v>
       </c>
     </row>
     <row r="3">
@@ -464,13 +464,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.26957</v>
+        <v>1.24898</v>
       </c>
       <c r="C3" t="n">
-        <v>0.43756</v>
+        <v>0.53463</v>
       </c>
       <c r="D3" t="n">
-        <v>0.56213</v>
+        <v>0.6556999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -478,13 +478,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.19085</v>
+        <v>1.18156</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5238</v>
+        <v>0.57262</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6495</v>
+        <v>0.69204</v>
       </c>
     </row>
     <row r="5">
@@ -492,13 +492,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.15674</v>
+        <v>1.19996</v>
       </c>
       <c r="C5" t="n">
-        <v>0.51857</v>
+        <v>0.5878100000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>0.64583</v>
+        <v>0.70209</v>
       </c>
     </row>
     <row r="6">
@@ -506,13 +506,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.11548</v>
+        <v>1.09277</v>
       </c>
       <c r="C6" t="n">
-        <v>0.56714</v>
+        <v>0.61835</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.73337</v>
       </c>
     </row>
     <row r="7">
@@ -520,13 +520,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.06686</v>
+        <v>1.05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.61214</v>
+        <v>0.66542</v>
       </c>
       <c r="D7" t="n">
-        <v>0.72932</v>
+        <v>0.77358</v>
       </c>
     </row>
     <row r="8">
@@ -534,13 +534,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.04013</v>
+        <v>1.00827</v>
       </c>
       <c r="C8" t="n">
-        <v>0.58635</v>
+        <v>0.66817</v>
       </c>
       <c r="D8" t="n">
-        <v>0.70764</v>
+        <v>0.77684</v>
       </c>
     </row>
     <row r="9">
@@ -548,13 +548,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.95723</v>
+        <v>0.98808</v>
       </c>
       <c r="C9" t="n">
-        <v>0.65626</v>
+        <v>0.66274</v>
       </c>
       <c r="D9" t="n">
-        <v>0.76798</v>
+        <v>0.7726</v>
       </c>
     </row>
     <row r="10">
@@ -562,13 +562,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.92335</v>
+        <v>0.93297</v>
       </c>
       <c r="C10" t="n">
-        <v>0.69314</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>0.79835</v>
+        <v>0.78485</v>
       </c>
     </row>
     <row r="11">
@@ -576,13 +576,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.91777</v>
+        <v>0.89442</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6881699999999999</v>
+        <v>0.70714</v>
       </c>
       <c r="D11" t="n">
-        <v>0.79457</v>
+        <v>0.80908</v>
       </c>
     </row>
     <row r="12">
@@ -590,13 +590,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.89029</v>
+        <v>0.87395</v>
       </c>
       <c r="C12" t="n">
-        <v>0.69643</v>
+        <v>0.68344</v>
       </c>
       <c r="D12" t="n">
-        <v>0.80104</v>
+        <v>0.79052</v>
       </c>
     </row>
     <row r="13">
@@ -604,13 +604,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.86056</v>
+        <v>0.84034</v>
       </c>
       <c r="C13" t="n">
-        <v>0.70155</v>
+        <v>0.70763</v>
       </c>
       <c r="D13" t="n">
-        <v>0.80543</v>
+        <v>0.81008</v>
       </c>
     </row>
     <row r="14">
@@ -618,13 +618,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.82331</v>
+        <v>0.8198800000000001</v>
       </c>
       <c r="C14" t="n">
-        <v>0.71989</v>
+        <v>0.7106</v>
       </c>
       <c r="D14" t="n">
-        <v>0.81994</v>
+        <v>0.8126</v>
       </c>
     </row>
     <row r="15">
@@ -632,13 +632,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7876</v>
+        <v>0.80499</v>
       </c>
       <c r="C15" t="n">
-        <v>0.74442</v>
+        <v>0.71179</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8386</v>
+        <v>0.81301</v>
       </c>
     </row>
     <row r="16">
@@ -646,13 +646,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.7764799999999999</v>
+        <v>0.76984</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7527199999999999</v>
+        <v>0.73508</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8446</v>
+        <v>0.8317</v>
       </c>
     </row>
     <row r="17">
@@ -660,13 +660,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.78348</v>
+        <v>0.77434</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7459</v>
+        <v>0.72709</v>
       </c>
       <c r="D17" t="n">
-        <v>0.83916</v>
+        <v>0.82544</v>
       </c>
     </row>
     <row r="18">
@@ -674,13 +674,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.75437</v>
+        <v>0.75021</v>
       </c>
       <c r="C18" t="n">
-        <v>0.74025</v>
+        <v>0.73189</v>
       </c>
       <c r="D18" t="n">
-        <v>0.83565</v>
+        <v>0.8293199999999999</v>
       </c>
     </row>
     <row r="19">
@@ -688,13 +688,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.7372</v>
+        <v>0.73116</v>
       </c>
       <c r="C19" t="n">
-        <v>0.75558</v>
+        <v>0.75322</v>
       </c>
       <c r="D19" t="n">
-        <v>0.84701</v>
+        <v>0.8453000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -702,13 +702,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.73103</v>
+        <v>0.72571</v>
       </c>
       <c r="C20" t="n">
-        <v>0.75761</v>
+        <v>0.75245</v>
       </c>
       <c r="D20" t="n">
-        <v>0.84855</v>
+        <v>0.8448</v>
       </c>
     </row>
     <row r="21">
@@ -716,13 +716,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.72865</v>
+        <v>0.71739</v>
       </c>
       <c r="C21" t="n">
-        <v>0.76098</v>
+        <v>0.75254</v>
       </c>
       <c r="D21" t="n">
-        <v>0.85084</v>
+        <v>0.84485</v>
       </c>
     </row>
     <row r="22">
@@ -730,13 +730,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>0.7099</v>
+        <v>0.7088100000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7631599999999999</v>
+        <v>0.75501</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8525700000000001</v>
+        <v>0.84678</v>
       </c>
     </row>
     <row r="23">
@@ -744,13 +744,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>0.70148</v>
+        <v>0.69865</v>
       </c>
       <c r="C23" t="n">
-        <v>0.75956</v>
+        <v>0.75837</v>
       </c>
       <c r="D23" t="n">
-        <v>0.85034</v>
+        <v>0.84944</v>
       </c>
     </row>
     <row r="24">
@@ -758,13 +758,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>0.69378</v>
+        <v>0.69575</v>
       </c>
       <c r="C24" t="n">
-        <v>0.77092</v>
+        <v>0.76149</v>
       </c>
       <c r="D24" t="n">
-        <v>0.85843</v>
+        <v>0.85173</v>
       </c>
     </row>
     <row r="25">
@@ -772,13 +772,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>0.70057</v>
+        <v>0.7033199999999999</v>
       </c>
       <c r="C25" t="n">
-        <v>0.76518</v>
+        <v>0.76276</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8541800000000001</v>
+        <v>0.85231</v>
       </c>
     </row>
     <row r="26">
@@ -786,13 +786,13 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>0.6781700000000001</v>
+        <v>0.68225</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7786</v>
+        <v>0.76554</v>
       </c>
       <c r="D26" t="n">
-        <v>0.86404</v>
+        <v>0.85473</v>
       </c>
     </row>
     <row r="27">
@@ -800,13 +800,13 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>0.67255</v>
+        <v>0.6785099999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7694299999999999</v>
+        <v>0.76695</v>
       </c>
       <c r="D27" t="n">
-        <v>0.85773</v>
+        <v>0.85582</v>
       </c>
     </row>
     <row r="28">
@@ -814,13 +814,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>0.73373</v>
+        <v>0.67364</v>
       </c>
       <c r="C28" t="n">
-        <v>0.74294</v>
+        <v>0.77097</v>
       </c>
       <c r="D28" t="n">
-        <v>0.83661</v>
+        <v>0.8587900000000001</v>
       </c>
     </row>
     <row r="29">
@@ -828,13 +828,13 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>0.67069</v>
+        <v>0.66804</v>
       </c>
       <c r="C29" t="n">
-        <v>0.77429</v>
+        <v>0.77359</v>
       </c>
       <c r="D29" t="n">
-        <v>0.86103</v>
+        <v>0.86067</v>
       </c>
     </row>
     <row r="30">
@@ -842,13 +842,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>0.66078</v>
+        <v>0.6781700000000001</v>
       </c>
       <c r="C30" t="n">
-        <v>0.78481</v>
+        <v>0.76794</v>
       </c>
       <c r="D30" t="n">
-        <v>0.86857</v>
+        <v>0.85638</v>
       </c>
     </row>
     <row r="31">
@@ -856,13 +856,13 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>0.6589699999999999</v>
+        <v>0.66021</v>
       </c>
       <c r="C31" t="n">
-        <v>0.77579</v>
+        <v>0.77214</v>
       </c>
       <c r="D31" t="n">
-        <v>0.86232</v>
+        <v>0.85977</v>
       </c>
     </row>
     <row r="32">
@@ -870,13 +870,13 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>0.66025</v>
+        <v>0.6637999999999999</v>
       </c>
       <c r="C32" t="n">
-        <v>0.77711</v>
+        <v>0.77171</v>
       </c>
       <c r="D32" t="n">
-        <v>0.86315</v>
+        <v>0.85931</v>
       </c>
     </row>
     <row r="33">
@@ -884,13 +884,13 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>0.65465</v>
+        <v>0.66168</v>
       </c>
       <c r="C33" t="n">
-        <v>0.77898</v>
+        <v>0.77639</v>
       </c>
       <c r="D33" t="n">
-        <v>0.86452</v>
+        <v>0.86271</v>
       </c>
     </row>
     <row r="34">
@@ -898,13 +898,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>0.65113</v>
+        <v>0.66303</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7790899999999999</v>
+        <v>0.77795</v>
       </c>
       <c r="D34" t="n">
-        <v>0.86469</v>
+        <v>0.86359</v>
       </c>
     </row>
     <row r="35">
@@ -912,13 +912,13 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>0.65444</v>
+        <v>0.65639</v>
       </c>
       <c r="C35" t="n">
-        <v>0.77781</v>
+        <v>0.7784</v>
       </c>
       <c r="D35" t="n">
-        <v>0.86378</v>
+        <v>0.86411</v>
       </c>
     </row>
     <row r="36">
@@ -926,13 +926,13 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>0.65154</v>
+        <v>0.65211</v>
       </c>
       <c r="C36" t="n">
-        <v>0.77423</v>
+        <v>0.78309</v>
       </c>
       <c r="D36" t="n">
-        <v>0.86115</v>
+        <v>0.86753</v>
       </c>
     </row>
     <row r="37">
@@ -940,13 +940,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>0.65161</v>
+        <v>0.64883</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7801</v>
+        <v>0.78312</v>
       </c>
       <c r="D37" t="n">
-        <v>0.86538</v>
+        <v>0.86758</v>
       </c>
     </row>
     <row r="38">
@@ -954,13 +954,13 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>0.64612</v>
+        <v>0.64458</v>
       </c>
       <c r="C38" t="n">
-        <v>0.7825800000000001</v>
+        <v>0.77876</v>
       </c>
       <c r="D38" t="n">
-        <v>0.8672</v>
+        <v>0.8646</v>
       </c>
     </row>
     <row r="39">
@@ -968,13 +968,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>0.64481</v>
+        <v>0.65287</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7850200000000001</v>
+        <v>0.77847</v>
       </c>
       <c r="D39" t="n">
-        <v>0.86895</v>
+        <v>0.86426</v>
       </c>
     </row>
     <row r="40">
@@ -982,13 +982,13 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>0.64275</v>
+        <v>0.64134</v>
       </c>
       <c r="C40" t="n">
-        <v>0.77799</v>
+        <v>0.78472</v>
       </c>
       <c r="D40" t="n">
-        <v>0.86391</v>
+        <v>0.86883</v>
       </c>
     </row>
     <row r="41">
@@ -996,13 +996,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>0.63528</v>
+        <v>0.64477</v>
       </c>
       <c r="C41" t="n">
-        <v>0.78396</v>
+        <v>0.78565</v>
       </c>
       <c r="D41" t="n">
-        <v>0.86837</v>
+        <v>0.86943</v>
       </c>
     </row>
     <row r="42">
@@ -1010,13 +1010,13 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>0.64069</v>
+        <v>0.63841</v>
       </c>
       <c r="C42" t="n">
-        <v>0.78646</v>
+        <v>0.78733</v>
       </c>
       <c r="D42" t="n">
-        <v>0.86991</v>
+        <v>0.8706700000000001</v>
       </c>
     </row>
     <row r="43">
@@ -1024,13 +1024,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>0.63969</v>
+        <v>0.6412099999999999</v>
       </c>
       <c r="C43" t="n">
-        <v>0.78791</v>
+        <v>0.77961</v>
       </c>
       <c r="D43" t="n">
-        <v>0.87095</v>
+        <v>0.8651799999999999</v>
       </c>
     </row>
     <row r="44">
@@ -1038,13 +1038,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>0.63442</v>
+        <v>0.63285</v>
       </c>
       <c r="C44" t="n">
-        <v>0.78987</v>
+        <v>0.7896</v>
       </c>
       <c r="D44" t="n">
-        <v>0.87242</v>
+        <v>0.87229</v>
       </c>
     </row>
     <row r="45">
@@ -1052,13 +1052,13 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>0.63217</v>
+        <v>0.64127</v>
       </c>
       <c r="C45" t="n">
-        <v>0.79433</v>
+        <v>0.78023</v>
       </c>
       <c r="D45" t="n">
-        <v>0.87549</v>
+        <v>0.86557</v>
       </c>
     </row>
     <row r="46">
@@ -1066,13 +1066,13 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>0.64376</v>
+        <v>0.6307700000000001</v>
       </c>
       <c r="C46" t="n">
-        <v>0.78607</v>
+        <v>0.78835</v>
       </c>
       <c r="D46" t="n">
-        <v>0.86961</v>
+        <v>0.87144</v>
       </c>
     </row>
     <row r="47">
@@ -1080,13 +1080,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>0.63297</v>
+        <v>0.63027</v>
       </c>
       <c r="C47" t="n">
-        <v>0.79122</v>
+        <v>0.79372</v>
       </c>
       <c r="D47" t="n">
-        <v>0.87331</v>
+        <v>0.8752</v>
       </c>
     </row>
     <row r="48">
@@ -1094,13 +1094,13 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>0.63086</v>
+        <v>0.63476</v>
       </c>
       <c r="C48" t="n">
-        <v>0.79178</v>
+        <v>0.78138</v>
       </c>
       <c r="D48" t="n">
-        <v>0.87371</v>
+        <v>0.8666700000000001</v>
       </c>
     </row>
     <row r="49">
@@ -1108,13 +1108,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>0.62747</v>
+        <v>0.62987</v>
       </c>
       <c r="C49" t="n">
-        <v>0.79375</v>
+        <v>0.79269</v>
       </c>
       <c r="D49" t="n">
-        <v>0.87513</v>
+        <v>0.87446</v>
       </c>
     </row>
     <row r="50">
@@ -1122,13 +1122,13 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>0.6291600000000001</v>
+        <v>0.63854</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7966</v>
+        <v>0.78486</v>
       </c>
       <c r="D50" t="n">
-        <v>0.87705</v>
+        <v>0.86891</v>
       </c>
     </row>
     <row r="51">
@@ -1136,13 +1136,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>0.6252799999999999</v>
+        <v>0.63528</v>
       </c>
       <c r="C51" t="n">
-        <v>0.7950199999999999</v>
+        <v>0.79495</v>
       </c>
       <c r="D51" t="n">
-        <v>0.87603</v>
+        <v>0.87577</v>
       </c>
     </row>
   </sheetData>
